--- a/app/src/main/assets/Jet_Template.xlsx
+++ b/app/src/main/assets/Jet_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\MC_V4\app\src\main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0778534F-D765-45EE-9A97-160233C6AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00B298E-24F8-4034-BA61-755137049962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{B67490F5-CAA8-4044-9146-29D6D0F9BA8B}"/>
   </bookViews>

--- a/app/src/main/assets/Jet_Template.xlsx
+++ b/app/src/main/assets/Jet_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\MC_V4\app\src\main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00B298E-24F8-4034-BA61-755137049962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15E58A6-B883-4666-AFA5-694886840257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{B67490F5-CAA8-4044-9146-29D6D0F9BA8B}"/>
   </bookViews>
